--- a/mosip_master/xlsx/dynamic_field.xlsx
+++ b/mosip_master/xlsx/dynamic_field.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -159,12 +159,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -814,7 +813,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -832,10 +831,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1155,7 +1150,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="8.57142857142857" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5714285714286" customWidth="1"/>
@@ -1459,426 +1454,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="E11" s="7"/>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="E12" s="7"/>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="E13" s="7"/>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="E14" s="7"/>
-      <c r="G14" s="8"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="E15" s="7"/>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="E16" s="7"/>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="E17" s="7"/>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="E18" s="7"/>
-      <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="E19" s="7"/>
-      <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="E20" s="7"/>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="E21" s="7"/>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="E22" s="7"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="E23" s="7"/>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="E24" s="7"/>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="E25" s="7"/>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="E26" s="7"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="E27" s="7"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="E28" s="7"/>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="E29" s="7"/>
-      <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="E30" s="7"/>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="E35" s="7"/>
-      <c r="G35" s="8"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="E36" s="7"/>
-      <c r="G36" s="8"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="E37" s="7"/>
-      <c r="G37" s="8"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="E38" s="7"/>
-      <c r="G38" s="8"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="E39" s="7"/>
-      <c r="G39" s="8"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="E40" s="7"/>
-      <c r="G40" s="8"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="E41" s="7"/>
-      <c r="G41" s="8"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="E42" s="7"/>
-      <c r="G42" s="8"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="E43" s="7"/>
-      <c r="G43" s="8"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="E44" s="7"/>
-      <c r="G44" s="8"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="E45" s="7"/>
-      <c r="G45" s="8"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="E46" s="7"/>
-      <c r="G46" s="8"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="E47" s="7"/>
-      <c r="G47" s="8"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="E48" s="7"/>
-      <c r="G48" s="8"/>
-    </row>
-    <row r="49" spans="5:7">
-      <c r="E49" s="7"/>
-      <c r="G49" s="8"/>
-    </row>
-    <row r="50" spans="5:7">
-      <c r="E50" s="7"/>
-      <c r="G50" s="8"/>
-    </row>
-    <row r="51" spans="5:7">
-      <c r="E51" s="7"/>
-      <c r="G51" s="8"/>
-    </row>
-    <row r="52" spans="5:7">
-      <c r="E52" s="7"/>
-      <c r="G52" s="8"/>
-    </row>
-    <row r="53" spans="5:7">
-      <c r="E53" s="7"/>
-      <c r="G53" s="8"/>
-    </row>
-    <row r="54" spans="5:7">
-      <c r="E54" s="7"/>
-      <c r="G54" s="8"/>
-    </row>
-    <row r="55" spans="5:7">
-      <c r="E55" s="7"/>
-      <c r="G55" s="8"/>
-    </row>
-    <row r="56" spans="5:7">
-      <c r="E56" s="7"/>
-      <c r="G56" s="8"/>
-    </row>
-    <row r="57" spans="5:7">
-      <c r="E57" s="7"/>
-      <c r="G57" s="8"/>
-    </row>
-    <row r="58" spans="5:7">
-      <c r="E58" s="7"/>
-      <c r="G58" s="8"/>
-    </row>
-    <row r="59" spans="5:7">
-      <c r="E59" s="7"/>
-      <c r="G59" s="8"/>
-    </row>
-    <row r="60" spans="5:7">
-      <c r="E60" s="7"/>
-      <c r="G60" s="8"/>
-    </row>
-    <row r="61" spans="5:7">
-      <c r="E61" s="7"/>
-      <c r="G61" s="8"/>
-    </row>
-    <row r="62" spans="5:7">
-      <c r="E62" s="7"/>
-      <c r="G62" s="8"/>
-    </row>
-    <row r="63" spans="5:7">
-      <c r="E63" s="7"/>
-      <c r="G63" s="8"/>
-    </row>
-    <row r="64" spans="5:7">
-      <c r="E64" s="7"/>
-      <c r="G64" s="8"/>
-    </row>
-    <row r="65" spans="5:7">
-      <c r="E65" s="7"/>
-      <c r="G65" s="8"/>
-    </row>
-    <row r="66" spans="5:7">
-      <c r="E66" s="7"/>
-      <c r="G66" s="8"/>
-    </row>
-    <row r="67" spans="5:7">
-      <c r="E67" s="7"/>
-      <c r="G67" s="8"/>
-    </row>
-    <row r="68" spans="5:7">
-      <c r="E68" s="7"/>
-      <c r="G68" s="8"/>
-    </row>
-    <row r="69" spans="5:7">
-      <c r="E69" s="7"/>
-      <c r="G69" s="8"/>
-    </row>
-    <row r="70" spans="5:7">
-      <c r="E70" s="7"/>
-      <c r="G70" s="8"/>
-    </row>
-    <row r="71" spans="5:7">
-      <c r="E71" s="7"/>
-      <c r="G71" s="8"/>
-    </row>
-    <row r="72" spans="5:7">
-      <c r="E72" s="7"/>
-      <c r="G72" s="8"/>
-    </row>
-    <row r="73" spans="5:7">
-      <c r="E73" s="7"/>
-      <c r="G73" s="8"/>
-    </row>
-    <row r="74" spans="5:7">
-      <c r="E74" s="7"/>
-      <c r="G74" s="8"/>
-    </row>
-    <row r="75" spans="5:7">
-      <c r="E75" s="7"/>
-      <c r="G75" s="8"/>
-    </row>
-    <row r="76" spans="5:7">
-      <c r="E76" s="7"/>
-      <c r="G76" s="8"/>
-    </row>
-    <row r="77" spans="5:7">
-      <c r="E77" s="7"/>
-      <c r="G77" s="8"/>
-    </row>
-    <row r="78" spans="5:7">
-      <c r="E78" s="7"/>
-      <c r="G78" s="8"/>
-    </row>
-    <row r="79" spans="5:7">
-      <c r="E79" s="7"/>
-      <c r="G79" s="8"/>
-    </row>
-    <row r="80" spans="5:7">
-      <c r="E80" s="7"/>
-      <c r="G80" s="8"/>
-    </row>
-    <row r="81" spans="5:7">
-      <c r="E81" s="7"/>
-      <c r="G81" s="8"/>
-    </row>
-    <row r="82" spans="5:7">
-      <c r="E82" s="7"/>
-      <c r="G82" s="8"/>
-    </row>
-    <row r="83" spans="5:7">
-      <c r="E83" s="7"/>
-      <c r="G83" s="8"/>
-    </row>
-    <row r="84" spans="5:7">
-      <c r="E84" s="7"/>
-      <c r="G84" s="8"/>
-    </row>
-    <row r="85" spans="5:7">
-      <c r="E85" s="7"/>
-      <c r="G85" s="8"/>
-    </row>
-    <row r="86" spans="5:7">
-      <c r="E86" s="7"/>
-      <c r="G86" s="8"/>
-    </row>
-    <row r="87" spans="5:7">
-      <c r="E87" s="7"/>
-      <c r="G87" s="8"/>
-    </row>
-    <row r="88" spans="5:7">
-      <c r="E88" s="7"/>
-      <c r="G88" s="8"/>
-    </row>
-    <row r="89" spans="5:7">
-      <c r="E89" s="7"/>
-      <c r="G89" s="8"/>
-    </row>
-    <row r="90" spans="5:7">
-      <c r="E90" s="7"/>
-      <c r="G90" s="8"/>
-    </row>
-    <row r="91" spans="5:7">
-      <c r="E91" s="7"/>
-      <c r="G91" s="8"/>
-    </row>
-    <row r="92" spans="5:7">
-      <c r="E92" s="7"/>
-      <c r="G92" s="8"/>
-    </row>
-    <row r="93" spans="5:7">
-      <c r="E93" s="7"/>
-      <c r="G93" s="8"/>
-    </row>
-    <row r="94" spans="5:7">
-      <c r="E94" s="7"/>
-      <c r="G94" s="8"/>
-    </row>
-    <row r="95" spans="5:7">
-      <c r="E95" s="7"/>
-      <c r="G95" s="8"/>
-    </row>
-    <row r="96" spans="5:7">
-      <c r="E96" s="7"/>
-      <c r="G96" s="8"/>
-    </row>
-    <row r="97" spans="2:9">
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7"/>
-    </row>
-    <row r="98" spans="2:9">
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="7"/>
-      <c r="I98" s="7"/>
-    </row>
-    <row r="99" spans="2:9">
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="7"/>
-    </row>
-    <row r="100" spans="2:9">
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7"/>
-    </row>
-    <row r="101" spans="2:9">
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I101" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I10" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
